--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Downloads\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4D10AAE-3E70-4590-9B43-EB78763F186B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A144B873-A8D8-4C3A-9CAE-6A6A2B421201}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -240,6 +240,9 @@
   <si>
     <t>it's a peaceful Sunday and I am feeling very good and relaxed today.</t>
   </si>
+  <si>
+    <t>17/08/2026</t>
+  </si>
 </sst>
 </file>
 
@@ -248,7 +251,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -327,6 +330,12 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -1340,26 +1349,50 @@
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+      <c r="A13" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="B13" s="14">
+        <v>510</v>
+      </c>
+      <c r="C13" s="14">
+        <v>60</v>
+      </c>
+      <c r="D13" s="14">
+        <v>120</v>
+      </c>
+      <c r="E13" s="14">
+        <v>90</v>
+      </c>
+      <c r="F13" s="14">
+        <v>250</v>
+      </c>
+      <c r="G13" s="14">
+        <v>5</v>
+      </c>
+      <c r="H13" s="14">
+        <v>120</v>
+      </c>
+      <c r="I13" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>1150</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
+        <v>290</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N13" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="13"/>
@@ -9906,6 +9939,7 @@
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="F3:G3"/>
   </mergeCells>
+  <phoneticPr fontId="12" type="noConversion"/>
   <conditionalFormatting sqref="J6:J401">
     <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
       <formula>0</formula>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Downloads\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A144B873-A8D8-4C3A-9CAE-6A6A2B421201}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6CFA679-7D17-4E8D-BE67-F4EC30E1AAC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="70">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -242,6 +242,9 @@
   </si>
   <si>
     <t>17/08/2026</t>
+  </si>
+  <si>
+    <t>18/08/2026</t>
   </si>
 </sst>
 </file>
@@ -1395,26 +1398,50 @@
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+      <c r="A14" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="B14" s="14">
+        <v>510</v>
+      </c>
+      <c r="C14" s="14">
+        <v>60</v>
+      </c>
+      <c r="D14" s="14">
+        <v>120</v>
+      </c>
+      <c r="E14" s="14">
+        <v>90</v>
+      </c>
+      <c r="F14" s="14">
+        <v>300</v>
+      </c>
+      <c r="G14" s="14">
+        <v>6</v>
+      </c>
+      <c r="H14" s="14">
+        <v>120</v>
+      </c>
+      <c r="I14" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>1200</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="17"/>
+        <v>240</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N14" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="13"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Downloads\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6CFA679-7D17-4E8D-BE67-F4EC30E1AAC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1815742-D5D1-4BD3-92D3-C5D0619F3234}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="71">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -245,6 +245,9 @@
   </si>
   <si>
     <t>18/08/2026</t>
+  </si>
+  <si>
+    <t>19/08/2026</t>
   </si>
 </sst>
 </file>
@@ -1444,26 +1447,50 @@
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+      <c r="A15" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="B15" s="14">
+        <v>540</v>
+      </c>
+      <c r="C15" s="14">
+        <v>50</v>
+      </c>
+      <c r="D15" s="14">
+        <v>120</v>
+      </c>
+      <c r="E15" s="14">
+        <v>90</v>
+      </c>
+      <c r="F15" s="14">
+        <v>300</v>
+      </c>
+      <c r="G15" s="14">
+        <v>6</v>
+      </c>
+      <c r="H15" s="14">
+        <v>120</v>
+      </c>
+      <c r="I15" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>1220</v>
+      </c>
+      <c r="J15" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="17"/>
+        <v>220</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N15" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="13"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Downloads\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1815742-D5D1-4BD3-92D3-C5D0619F3234}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50BE72B0-0EC9-465E-B613-86426AA3A27A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="72">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -248,6 +248,9 @@
   </si>
   <si>
     <t>19/08/2026</t>
+  </si>
+  <si>
+    <t>20/08/2026</t>
   </si>
 </sst>
 </file>
@@ -1493,26 +1496,50 @@
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+      <c r="A16" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="B16" s="14">
+        <v>570</v>
+      </c>
+      <c r="C16" s="14">
+        <v>60</v>
+      </c>
+      <c r="D16" s="14">
+        <v>120</v>
+      </c>
+      <c r="E16" s="14">
+        <v>90</v>
+      </c>
+      <c r="F16" s="14">
+        <v>250</v>
+      </c>
+      <c r="G16" s="14">
+        <v>5</v>
+      </c>
+      <c r="H16" s="14">
+        <v>120</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>1210</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="17"/>
+        <v>230</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="13"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Downloads\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50BE72B0-0EC9-465E-B613-86426AA3A27A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD4D7332-CCD7-439F-928B-6539CFB2713F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="74">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -251,6 +251,12 @@
   </si>
   <si>
     <t>20/08/2026</t>
+  </si>
+  <si>
+    <t>21/08/2026</t>
+  </si>
+  <si>
+    <t>22/08/2026</t>
   </si>
 </sst>
 </file>
@@ -1542,48 +1548,94 @@
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+      <c r="A17" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="B17" s="14">
+        <v>570</v>
+      </c>
+      <c r="C17" s="14">
+        <v>60</v>
+      </c>
+      <c r="D17" s="14">
+        <v>120</v>
+      </c>
+      <c r="E17" s="14">
+        <v>60</v>
+      </c>
+      <c r="F17" s="14">
+        <v>200</v>
+      </c>
+      <c r="G17" s="14">
+        <v>4</v>
+      </c>
+      <c r="H17" s="14">
+        <v>120</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>1130</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
+        <v>310</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="13"/>
+      <c r="A18" s="13" t="s">
+        <v>73</v>
+      </c>
       <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+      <c r="C18" s="14">
+        <v>60</v>
+      </c>
+      <c r="D18" s="14">
+        <v>120</v>
+      </c>
+      <c r="E18" s="14">
+        <v>50</v>
+      </c>
+      <c r="F18" s="14">
+        <v>0</v>
+      </c>
+      <c r="G18" s="14">
+        <v>0</v>
+      </c>
+      <c r="H18" s="14">
+        <v>180</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>410</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="17"/>
+        <v>1030</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="13"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Downloads\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD4D7332-CCD7-439F-928B-6539CFB2713F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5616C257-3361-4C42-AB8A-9888F36791F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="75">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -257,6 +257,9 @@
   </si>
   <si>
     <t>22/08/2026</t>
+  </si>
+  <si>
+    <t>23/08/2026</t>
   </si>
 </sst>
 </file>
@@ -1638,26 +1641,46 @@
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="13"/>
+      <c r="A19" s="13" t="s">
+        <v>74</v>
+      </c>
       <c r="B19" s="14"/>
       <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+      <c r="D19" s="14">
+        <v>120</v>
+      </c>
+      <c r="E19" s="14">
+        <v>90</v>
+      </c>
+      <c r="F19" s="14">
+        <v>0</v>
+      </c>
+      <c r="G19" s="14">
+        <v>0</v>
+      </c>
+      <c r="H19" s="14">
+        <v>180</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>390</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
+        <v>1050</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="13"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Downloads\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5616C257-3361-4C42-AB8A-9888F36791F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32741560-8435-4011-8D1B-9B9DC521B566}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="76">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -260,6 +260,9 @@
   </si>
   <si>
     <t>23/08/2026</t>
+  </si>
+  <si>
+    <t>24/08/2026</t>
   </si>
 </sst>
 </file>
@@ -1683,26 +1686,46 @@
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="13"/>
+      <c r="A20" s="13" t="s">
+        <v>75</v>
+      </c>
       <c r="B20" s="14"/>
       <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+      <c r="D20" s="14">
+        <v>120</v>
+      </c>
+      <c r="E20" s="14">
+        <v>40</v>
+      </c>
+      <c r="F20" s="14">
+        <v>250</v>
+      </c>
+      <c r="G20" s="14">
+        <v>5</v>
+      </c>
+      <c r="H20" s="14">
+        <v>190</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>600</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="17"/>
+        <v>840</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="13"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Downloads\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32741560-8435-4011-8D1B-9B9DC521B566}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C4370AC-37FA-4FCE-B2E9-346C90272B7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="77">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -263,6 +263,9 @@
   </si>
   <si>
     <t>24/08/2026</t>
+  </si>
+  <si>
+    <t>25/08/2026</t>
   </si>
 </sst>
 </file>
@@ -1728,26 +1731,46 @@
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="13"/>
+      <c r="A21" s="13" t="s">
+        <v>76</v>
+      </c>
       <c r="B21" s="14"/>
       <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+      <c r="D21" s="14">
+        <v>120</v>
+      </c>
+      <c r="E21" s="14">
+        <v>90</v>
+      </c>
+      <c r="F21" s="14">
+        <v>350</v>
+      </c>
+      <c r="G21" s="14">
+        <v>7</v>
+      </c>
+      <c r="H21" s="14">
+        <v>120</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>680</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
+        <v>760</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="13"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Downloads\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C4370AC-37FA-4FCE-B2E9-346C90272B7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBEE8002-EC70-4978-9331-F372A77E8DD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="78">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -266,6 +266,9 @@
   </si>
   <si>
     <t>25/08/2026</t>
+  </si>
+  <si>
+    <t>26/08/2026</t>
   </si>
 </sst>
 </file>
@@ -1773,26 +1776,46 @@
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="13"/>
+      <c r="A22" s="13" t="s">
+        <v>77</v>
+      </c>
       <c r="B22" s="14"/>
       <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+      <c r="D22" s="14">
+        <v>120</v>
+      </c>
+      <c r="E22" s="14">
+        <v>90</v>
+      </c>
+      <c r="F22" s="14">
+        <v>300</v>
+      </c>
+      <c r="G22" s="14">
+        <v>6</v>
+      </c>
+      <c r="H22" s="14">
+        <v>120</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>630</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="17"/>
+        <v>810</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="13"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Downloads\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBEE8002-EC70-4978-9331-F372A77E8DD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1487B6AC-6546-44CD-849C-2090DD156A15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -269,6 +269,9 @@
   </si>
   <si>
     <t>26/08/2026</t>
+  </si>
+  <si>
+    <t>27/08/2026</t>
   </si>
 </sst>
 </file>
@@ -1818,26 +1821,46 @@
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="13"/>
+      <c r="A23" s="13" t="s">
+        <v>78</v>
+      </c>
       <c r="B23" s="14"/>
       <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+      <c r="D23" s="14">
+        <v>120</v>
+      </c>
+      <c r="E23" s="14">
+        <v>90</v>
+      </c>
+      <c r="F23" s="14">
+        <v>350</v>
+      </c>
+      <c r="G23" s="14">
+        <v>7</v>
+      </c>
+      <c r="H23" s="14">
+        <v>120</v>
+      </c>
+      <c r="I23" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>680</v>
+      </c>
+      <c r="J23" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="17"/>
+        <v>760</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="13"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Downloads\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1487B6AC-6546-44CD-849C-2090DD156A15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E05E1B71-DB8D-4976-BA22-46C87A523446}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="81">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -272,6 +272,12 @@
   </si>
   <si>
     <t>27/08/2026</t>
+  </si>
+  <si>
+    <t>28/08/2026</t>
+  </si>
+  <si>
+    <t>29/08/2026</t>
   </si>
 </sst>
 </file>
@@ -1863,48 +1869,80 @@
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="13"/>
+      <c r="A24" s="13" t="s">
+        <v>79</v>
+      </c>
       <c r="B24" s="14"/>
       <c r="C24" s="14"/>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+      <c r="F24" s="14">
+        <v>300</v>
+      </c>
+      <c r="G24" s="14">
+        <v>6</v>
+      </c>
+      <c r="H24" s="14">
+        <v>120</v>
+      </c>
+      <c r="I24" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>420</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="17"/>
+        <v>1020</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="13"/>
+      <c r="A25" s="13" t="s">
+        <v>80</v>
+      </c>
       <c r="B25" s="14"/>
       <c r="C25" s="14"/>
       <c r="D25" s="14"/>
       <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
+      <c r="F25" s="14">
+        <v>0</v>
+      </c>
+      <c r="G25" s="14">
+        <v>0</v>
+      </c>
+      <c r="H25" s="14">
+        <v>180</v>
+      </c>
+      <c r="I25" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>180</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="17"/>
+        <v>1260</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N25" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="13"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Downloads\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E05E1B71-DB8D-4976-BA22-46C87A523446}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71F6D3A9-8AFF-4DAA-8DC8-CBCDFA0C8AD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="82">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -278,6 +278,9 @@
   </si>
   <si>
     <t>29/08/2026</t>
+  </si>
+  <si>
+    <t>30/08/2026</t>
   </si>
 </sst>
 </file>
@@ -1618,7 +1621,9 @@
       <c r="A18" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="B18" s="14"/>
+      <c r="B18" s="14">
+        <v>570</v>
+      </c>
       <c r="C18" s="14">
         <v>60</v>
       </c>
@@ -1639,11 +1644,11 @@
       </c>
       <c r="I18" s="15">
         <f t="shared" si="1"/>
-        <v>410</v>
+        <v>980</v>
       </c>
       <c r="J18" s="15">
         <f t="shared" si="0"/>
-        <v>1030</v>
+        <v>460</v>
       </c>
       <c r="K18" s="16" t="s">
         <v>49</v>
@@ -1662,8 +1667,12 @@
       <c r="A19" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
+      <c r="B19" s="14">
+        <v>570</v>
+      </c>
+      <c r="C19" s="14">
+        <v>60</v>
+      </c>
       <c r="D19" s="14">
         <v>120</v>
       </c>
@@ -1681,11 +1690,11 @@
       </c>
       <c r="I19" s="15">
         <f t="shared" si="1"/>
-        <v>390</v>
+        <v>1020</v>
       </c>
       <c r="J19" s="15">
         <f t="shared" si="0"/>
-        <v>1050</v>
+        <v>420</v>
       </c>
       <c r="K19" s="16" t="s">
         <v>49</v>
@@ -1704,8 +1713,12 @@
       <c r="A20" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
+      <c r="B20" s="14">
+        <v>570</v>
+      </c>
+      <c r="C20" s="14">
+        <v>60</v>
+      </c>
       <c r="D20" s="14">
         <v>120</v>
       </c>
@@ -1723,11 +1736,11 @@
       </c>
       <c r="I20" s="15">
         <f t="shared" si="1"/>
-        <v>600</v>
+        <v>1230</v>
       </c>
       <c r="J20" s="15">
         <f t="shared" si="0"/>
-        <v>840</v>
+        <v>210</v>
       </c>
       <c r="K20" s="16" t="s">
         <v>62</v>
@@ -1746,8 +1759,12 @@
       <c r="A21" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
+      <c r="B21" s="14">
+        <v>570</v>
+      </c>
+      <c r="C21" s="14">
+        <v>60</v>
+      </c>
       <c r="D21" s="14">
         <v>120</v>
       </c>
@@ -1765,11 +1782,11 @@
       </c>
       <c r="I21" s="15">
         <f t="shared" si="1"/>
-        <v>680</v>
+        <v>1310</v>
       </c>
       <c r="J21" s="15">
         <f t="shared" si="0"/>
-        <v>760</v>
+        <v>130</v>
       </c>
       <c r="K21" s="16" t="s">
         <v>62</v>
@@ -1788,8 +1805,12 @@
       <c r="A22" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
+      <c r="B22" s="14">
+        <v>570</v>
+      </c>
+      <c r="C22" s="14">
+        <v>60</v>
+      </c>
       <c r="D22" s="14">
         <v>120</v>
       </c>
@@ -1807,11 +1828,11 @@
       </c>
       <c r="I22" s="15">
         <f t="shared" si="1"/>
-        <v>630</v>
+        <v>1260</v>
       </c>
       <c r="J22" s="15">
         <f t="shared" si="0"/>
-        <v>810</v>
+        <v>180</v>
       </c>
       <c r="K22" s="16" t="s">
         <v>62</v>
@@ -1830,8 +1851,12 @@
       <c r="A23" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
+      <c r="B23" s="14">
+        <v>570</v>
+      </c>
+      <c r="C23" s="14">
+        <v>60</v>
+      </c>
       <c r="D23" s="14">
         <v>120</v>
       </c>
@@ -1849,11 +1874,11 @@
       </c>
       <c r="I23" s="15">
         <f t="shared" si="1"/>
-        <v>680</v>
+        <v>1310</v>
       </c>
       <c r="J23" s="15">
         <f t="shared" si="0"/>
-        <v>760</v>
+        <v>130</v>
       </c>
       <c r="K23" s="16" t="s">
         <v>49</v>
@@ -1872,10 +1897,18 @@
       <c r="A24" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
+      <c r="B24" s="14">
+        <v>570</v>
+      </c>
+      <c r="C24" s="14">
+        <v>60</v>
+      </c>
+      <c r="D24" s="14">
+        <v>120</v>
+      </c>
+      <c r="E24" s="14">
+        <v>90</v>
+      </c>
       <c r="F24" s="14">
         <v>300</v>
       </c>
@@ -1887,11 +1920,11 @@
       </c>
       <c r="I24" s="15">
         <f t="shared" si="1"/>
-        <v>420</v>
+        <v>1260</v>
       </c>
       <c r="J24" s="15">
         <f t="shared" si="0"/>
-        <v>1020</v>
+        <v>180</v>
       </c>
       <c r="K24" s="16" t="s">
         <v>62</v>
@@ -1910,10 +1943,18 @@
       <c r="A25" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
+      <c r="B25" s="14">
+        <v>570</v>
+      </c>
+      <c r="C25" s="14">
+        <v>60</v>
+      </c>
+      <c r="D25" s="14">
+        <v>180</v>
+      </c>
+      <c r="E25" s="14">
+        <v>50</v>
+      </c>
       <c r="F25" s="14">
         <v>0</v>
       </c>
@@ -1925,11 +1966,11 @@
       </c>
       <c r="I25" s="15">
         <f t="shared" si="1"/>
-        <v>180</v>
+        <v>1040</v>
       </c>
       <c r="J25" s="15">
         <f t="shared" si="0"/>
-        <v>1260</v>
+        <v>400</v>
       </c>
       <c r="K25" s="16" t="s">
         <v>49</v>
@@ -1945,26 +1986,50 @@
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+      <c r="A26" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="B26" s="14">
+        <v>590</v>
+      </c>
+      <c r="C26" s="14">
+        <v>50</v>
+      </c>
+      <c r="D26" s="14">
+        <v>190</v>
+      </c>
+      <c r="E26" s="14">
+        <v>40</v>
+      </c>
+      <c r="F26" s="14">
+        <v>0</v>
+      </c>
+      <c r="G26" s="14">
+        <v>0</v>
+      </c>
+      <c r="H26" s="14">
+        <v>120</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>990</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="17"/>
+        <v>450</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="13"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Downloads\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71F6D3A9-8AFF-4DAA-8DC8-CBCDFA0C8AD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6B00BED-3791-4D4A-B141-08F326835EB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="83">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -281,6 +281,9 @@
   </si>
   <si>
     <t>30/08/2026</t>
+  </si>
+  <si>
+    <t>31/08/2026</t>
   </si>
 </sst>
 </file>
@@ -2032,26 +2035,50 @@
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+      <c r="A27" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="B27" s="14">
+        <v>570</v>
+      </c>
+      <c r="C27" s="14">
+        <v>60</v>
+      </c>
+      <c r="D27" s="14">
+        <v>120</v>
+      </c>
+      <c r="E27" s="14">
+        <v>50</v>
+      </c>
+      <c r="F27" s="14">
+        <v>250</v>
+      </c>
+      <c r="G27" s="14">
+        <v>5</v>
+      </c>
+      <c r="H27" s="14">
+        <v>120</v>
+      </c>
+      <c r="I27" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>1170</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="17"/>
+        <v>270</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N27" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="13"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Downloads\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6B00BED-3791-4D4A-B141-08F326835EB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0AFC52F-64DE-4D7E-9F0B-E19C261C3082}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="83">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2081,26 +2081,50 @@
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+      <c r="A28" s="13">
+        <v>46031</v>
+      </c>
+      <c r="B28" s="14">
+        <v>570</v>
+      </c>
+      <c r="C28" s="14">
+        <v>60</v>
+      </c>
+      <c r="D28" s="14">
+        <v>120</v>
+      </c>
+      <c r="E28" s="14">
+        <v>50</v>
+      </c>
+      <c r="F28" s="14">
+        <v>350</v>
+      </c>
+      <c r="G28" s="14">
+        <v>7</v>
+      </c>
+      <c r="H28" s="14">
+        <v>130</v>
+      </c>
+      <c r="I28" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>1280</v>
+      </c>
+      <c r="J28" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="17"/>
+        <v>160</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="13"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Downloads\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0AFC52F-64DE-4D7E-9F0B-E19C261C3082}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07E16FA8-44CB-4FEF-8211-1628E03A8CBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="83">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2127,26 +2127,50 @@
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+      <c r="A29" s="13">
+        <v>46062</v>
+      </c>
+      <c r="B29" s="14">
+        <v>570</v>
+      </c>
+      <c r="C29" s="14">
+        <v>50</v>
+      </c>
+      <c r="D29" s="14">
+        <v>150</v>
+      </c>
+      <c r="E29" s="14">
+        <v>90</v>
+      </c>
+      <c r="F29" s="14">
+        <v>300</v>
+      </c>
+      <c r="G29" s="14">
+        <v>6</v>
+      </c>
+      <c r="H29" s="14">
+        <v>120</v>
+      </c>
+      <c r="I29" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>1280</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="17"/>
+        <v>160</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N29" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="13"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Downloads\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07E16FA8-44CB-4FEF-8211-1628E03A8CBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0C5C3F4-AE1F-412D-BB66-B257E22228DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="85">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -284,6 +284,12 @@
   </si>
   <si>
     <t>31/08/2026</t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Today is my ca exam of english comunication I felling very exited and learn new thing. </t>
   </si>
 </sst>
 </file>
@@ -2172,27 +2178,51 @@
         <v>66</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+    <row r="30" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A30" s="13">
+        <v>46090</v>
+      </c>
+      <c r="B30" s="14">
+        <v>570</v>
+      </c>
+      <c r="C30" s="14">
+        <v>60</v>
+      </c>
+      <c r="D30" s="14">
+        <v>120</v>
+      </c>
+      <c r="E30" s="14">
+        <v>50</v>
+      </c>
+      <c r="F30" s="14">
+        <v>200</v>
+      </c>
+      <c r="G30" s="14">
+        <v>4</v>
+      </c>
+      <c r="H30" s="14">
+        <v>130</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>1130</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="17"/>
+        <v>310</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N30" s="17" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="13"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Downloads\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0C5C3F4-AE1F-412D-BB66-B257E22228DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C2CB8B1-E6BC-442A-B0A5-83BDAFD5EB93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="86">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -290,6 +290,9 @@
   </si>
   <si>
     <t xml:space="preserve">Today is my ca exam of english comunication I felling very exited and learn new thing. </t>
+  </si>
+  <si>
+    <t>Today is my dbms practical exam of ca and my exam gone good.</t>
   </si>
 </sst>
 </file>
@@ -2224,27 +2227,51 @@
         <v>84</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+    <row r="31" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A31" s="13">
+        <v>46121</v>
+      </c>
+      <c r="B31" s="14">
+        <v>520</v>
+      </c>
+      <c r="C31" s="14">
+        <v>60</v>
+      </c>
+      <c r="D31" s="14">
+        <v>120</v>
+      </c>
+      <c r="E31" s="14">
+        <v>50</v>
+      </c>
+      <c r="F31" s="14">
+        <v>250</v>
+      </c>
+      <c r="G31" s="14">
+        <v>5</v>
+      </c>
+      <c r="H31" s="14">
+        <v>150</v>
+      </c>
+      <c r="I31" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>1150</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="17"/>
+        <v>290</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N31" s="17" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="13"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Downloads\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C2CB8B1-E6BC-442A-B0A5-83BDAFD5EB93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50EB0187-0C36-4CD3-A14F-A918C829DA2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="86">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2274,26 +2274,50 @@
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
+      <c r="A32" s="13">
+        <v>46151</v>
+      </c>
+      <c r="B32" s="14">
+        <v>580</v>
+      </c>
+      <c r="C32" s="14">
+        <v>60</v>
+      </c>
+      <c r="D32" s="14">
+        <v>150</v>
+      </c>
+      <c r="E32" s="14">
+        <v>50</v>
+      </c>
+      <c r="F32" s="14">
+        <v>0</v>
+      </c>
+      <c r="G32" s="14">
+        <v>0</v>
+      </c>
+      <c r="H32" s="14">
+        <v>160</v>
+      </c>
+      <c r="I32" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>1000</v>
+      </c>
+      <c r="J32" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="17"/>
+        <v>440</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N32" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="13"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Downloads\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50EB0187-0C36-4CD3-A14F-A918C829DA2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71BE7221-E73F-4CDF-9B74-BBE2C3964C42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="86">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2320,26 +2320,50 @@
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
+      <c r="A33" s="13">
+        <v>46182</v>
+      </c>
+      <c r="B33" s="14">
+        <v>580</v>
+      </c>
+      <c r="C33" s="14">
+        <v>50</v>
+      </c>
+      <c r="D33" s="14">
+        <v>150</v>
+      </c>
+      <c r="E33" s="14">
+        <v>90</v>
+      </c>
+      <c r="F33" s="14">
+        <v>0</v>
+      </c>
+      <c r="G33" s="14">
+        <v>0</v>
+      </c>
+      <c r="H33" s="14">
+        <v>180</v>
+      </c>
+      <c r="I33" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J33" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="17"/>
+        <v>390</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N33" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="13"/>
